--- a/Result/profitability/4946.xlsx
+++ b/Result/profitability/4946.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>4.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0.26875</v>
+        <v>0.8887499999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>25.33875</v>
+        <v>36.86625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.96</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8625</v>
+        <v>1.5025</v>
       </c>
       <c r="N3" t="n">
-        <v>39.50625</v>
+        <v>40.3975</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>1.17875</v>
+        <v>1.1625</v>
       </c>
       <c r="N4" t="n">
-        <v>43.11125</v>
+        <v>41.66375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>2.29</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1775</v>
+        <v>1.3075</v>
       </c>
       <c r="N5" t="n">
-        <v>44.82375</v>
+        <v>43.02500000000001</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.83</v>
       </c>
       <c r="M6" t="n">
-        <v>1.265</v>
+        <v>1.6325</v>
       </c>
       <c r="N6" t="n">
-        <v>45.67750000000001</v>
+        <v>45.1625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.77</v>
       </c>
       <c r="M7" t="n">
-        <v>1.5825</v>
+        <v>1.795</v>
       </c>
       <c r="N7" t="n">
-        <v>48.075</v>
+        <v>46.48125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-1.04</v>
       </c>
       <c r="M8" t="n">
-        <v>1.39375</v>
+        <v>1.61375</v>
       </c>
       <c r="N8" t="n">
-        <v>49.2425</v>
+        <v>47.71875</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4946</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>74</v>
+      </c>
+      <c r="D70" t="n">
+        <v>53</v>
+      </c>
+      <c r="E70" t="n">
+        <v>21</v>
+      </c>
+      <c r="F70" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-7</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-9.96%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>26</v>
+      </c>
+      <c r="J70" t="n">
+        <v>19</v>
+      </c>
+      <c r="K70" t="n">
+        <v>19</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-0.003749999999999976</v>
+      </c>
+      <c r="N70" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X70" t="n">
+        <v>4.292682926829269</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>-12.19</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>-0.3027819175360159</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0.9203539823008851</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>-14.39</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>-0.3389072067828545</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
